--- a/tests/fixtures/dq-project-fixture.xlsx
+++ b/tests/fixtures/dq-project-fixture.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DU95"/>
+  <dimension ref="A1:DV95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -753,27 +753,30 @@
         <v>Project Owner</v>
       </c>
       <c r="DN1" t="str">
+        <v>DC First Ship 1 Date</v>
+      </c>
+      <c r="DO1" t="str">
         <v>DC First Ship 2 Date</v>
       </c>
-      <c r="DO1" t="str">
+      <c r="DP1" t="str">
         <v>ProjectType</v>
       </c>
-      <c r="DP1" t="str">
+      <c r="DQ1" t="str">
         <v>ProjectOwnerResourceUID</v>
       </c>
-      <c r="DQ1" t="str">
+      <c r="DR1" t="str">
         <v>StageName</v>
       </c>
-      <c r="DR1" t="str">
+      <c r="DS1" t="str">
         <v>PhaseName</v>
       </c>
-      <c r="DS1" t="str">
+      <c r="DT1" t="str">
         <v>CurrentStage</v>
       </c>
-      <c r="DT1" t="str">
+      <c r="DU1" t="str">
         <v>CurrentPhase</v>
       </c>
-      <c r="DU1" t="str">
+      <c r="DV1" t="str">
         <v>ProjectUID</v>
       </c>
     </row>
@@ -793,9 +796,15 @@
       <c r="N2" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y2">
+        <v>7001000</v>
+      </c>
       <c r="AM2" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV2" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA2" t="str">
         <v>Incremental</v>
       </c>
@@ -836,27 +845,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN2" s="1">
+        <v>46193</v>
+      </c>
+      <c r="DO2" s="1">
         <v>46543</v>
       </c>
-      <c r="DO2" t="str">
+      <c r="DP2" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP2" t="str">
+      <c r="DQ2" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ2" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR2" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS2" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT2" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU2" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV2" t="str">
         <v>P-7001</v>
       </c>
     </row>
@@ -876,9 +888,15 @@
       <c r="N3" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y3">
+        <v>7002000</v>
+      </c>
       <c r="AM3" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV3" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA3" t="str">
         <v>Incremental</v>
       </c>
@@ -919,27 +937,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN3" s="1">
+        <v>46223</v>
+      </c>
+      <c r="DO3" s="1">
         <v>46573</v>
       </c>
-      <c r="DO3" t="str">
+      <c r="DP3" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP3" t="str">
+      <c r="DQ3" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ3" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR3" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS3" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT3" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU3" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV3" t="str">
         <v>P-7002</v>
       </c>
     </row>
@@ -959,9 +980,15 @@
       <c r="N4" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y4">
+        <v>7003000</v>
+      </c>
       <c r="AM4" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV4" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA4" t="str">
         <v>Incremental</v>
       </c>
@@ -1002,27 +1029,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN4" s="1">
+        <v>46254</v>
+      </c>
+      <c r="DO4" s="1">
         <v>46604</v>
       </c>
-      <c r="DO4" t="str">
+      <c r="DP4" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP4" t="str">
+      <c r="DQ4" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ4" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR4" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS4" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT4" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU4" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV4" t="str">
         <v>P-7003</v>
       </c>
     </row>
@@ -1042,9 +1072,15 @@
       <c r="N5" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y5">
+        <v>7004000</v>
+      </c>
       <c r="AM5" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV5" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA5" t="str">
         <v>Incremental</v>
       </c>
@@ -1085,27 +1121,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN5" s="1">
+        <v>46285</v>
+      </c>
+      <c r="DO5" s="1">
         <v>46635</v>
       </c>
-      <c r="DO5" t="str">
+      <c r="DP5" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP5" t="str">
+      <c r="DQ5" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ5" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR5" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS5" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT5" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU5" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV5" t="str">
         <v>P-7004</v>
       </c>
     </row>
@@ -1125,9 +1164,15 @@
       <c r="N6" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y6">
+        <v>7005000</v>
+      </c>
       <c r="AM6" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV6" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA6" t="str">
         <v>Incremental</v>
       </c>
@@ -1165,27 +1210,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN6" s="1">
+        <v>46315</v>
+      </c>
+      <c r="DO6" s="1">
         <v>46665</v>
       </c>
-      <c r="DO6" t="str">
+      <c r="DP6" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP6" t="str">
+      <c r="DQ6" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ6" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR6" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS6" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT6" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU6" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV6" t="str">
         <v>P-7005</v>
       </c>
     </row>
@@ -1205,9 +1253,15 @@
       <c r="N7" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y7">
+        <v>7006000</v>
+      </c>
       <c r="AM7" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV7" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA7" t="str">
         <v>Incremental</v>
       </c>
@@ -1245,27 +1299,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN7" s="1">
+        <v>46346</v>
+      </c>
+      <c r="DO7" s="1">
         <v>46696</v>
       </c>
-      <c r="DO7" t="str">
+      <c r="DP7" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP7" t="str">
+      <c r="DQ7" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ7" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR7" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS7" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT7" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU7" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV7" t="str">
         <v>P-7006</v>
       </c>
     </row>
@@ -1285,9 +1342,15 @@
       <c r="N8" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y8">
+        <v>7007000</v>
+      </c>
       <c r="AM8" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV8" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA8" t="str">
         <v>Incremental</v>
       </c>
@@ -1328,27 +1391,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN8" s="1">
+        <v>46376</v>
+      </c>
+      <c r="DO8" s="1">
         <v>46726</v>
       </c>
-      <c r="DO8" t="str">
+      <c r="DP8" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP8" t="str">
+      <c r="DQ8" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ8" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR8" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS8" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT8" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU8" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV8" t="str">
         <v>P-7007</v>
       </c>
     </row>
@@ -1368,9 +1434,15 @@
       <c r="N9" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y9">
+        <v>7008000</v>
+      </c>
       <c r="AM9" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV9" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA9" t="str">
         <v>Incremental</v>
       </c>
@@ -1396,27 +1468,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN9" s="1">
+        <v>46042</v>
+      </c>
+      <c r="DO9" s="1">
         <v>46392</v>
       </c>
-      <c r="DO9" t="str">
+      <c r="DP9" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP9" t="str">
+      <c r="DQ9" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ9" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR9" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS9" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT9" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU9" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV9" t="str">
         <v>P-7008</v>
       </c>
     </row>
@@ -1436,9 +1511,15 @@
       <c r="N10" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y10">
+        <v>7009000</v>
+      </c>
       <c r="AM10" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV10" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA10" t="str">
         <v>Improve</v>
       </c>
@@ -1470,27 +1551,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN10" s="1">
+        <v>46073</v>
+      </c>
+      <c r="DO10" s="1">
         <v>46423</v>
       </c>
-      <c r="DO10" t="str">
+      <c r="DP10" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP10" t="str">
+      <c r="DQ10" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ10" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR10" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS10" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT10" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU10" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV10" t="str">
         <v>P-7009</v>
       </c>
     </row>
@@ -1510,9 +1594,15 @@
       <c r="N11" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y11">
+        <v>7010000</v>
+      </c>
       <c r="AM11" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV11" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA11" t="str">
         <v>Improve</v>
       </c>
@@ -1547,27 +1637,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN11" s="1">
+        <v>46101</v>
+      </c>
+      <c r="DO11" s="1">
         <v>46451</v>
       </c>
-      <c r="DO11" t="str">
+      <c r="DP11" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP11" t="str">
+      <c r="DQ11" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ11" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR11" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS11" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT11" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU11" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV11" t="str">
         <v>P-7010</v>
       </c>
     </row>
@@ -1587,9 +1680,15 @@
       <c r="N12" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y12">
+        <v>7011000</v>
+      </c>
       <c r="AM12" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV12" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA12" t="str">
         <v>Improve</v>
       </c>
@@ -1624,27 +1723,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN12" s="1">
+        <v>46132</v>
+      </c>
+      <c r="DO12" s="1">
         <v>46482</v>
       </c>
-      <c r="DO12" t="str">
+      <c r="DP12" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP12" t="str">
+      <c r="DQ12" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ12" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR12" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS12" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT12" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU12" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV12" t="str">
         <v>P-7011</v>
       </c>
     </row>
@@ -1664,9 +1766,15 @@
       <c r="N13" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y13">
+        <v>7012000</v>
+      </c>
       <c r="AM13" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV13" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA13" t="str">
         <v>CRQ</v>
       </c>
@@ -1704,27 +1812,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN13" s="1">
+        <v>46162</v>
+      </c>
+      <c r="DO13" s="1">
         <v>46512</v>
       </c>
-      <c r="DO13" t="str">
+      <c r="DP13" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP13" t="str">
+      <c r="DQ13" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ13" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR13" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS13" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT13" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU13" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV13" t="str">
         <v>P-7012</v>
       </c>
     </row>
@@ -1744,9 +1855,15 @@
       <c r="N14" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y14">
+        <v>7013000</v>
+      </c>
       <c r="AM14" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV14" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA14" t="str">
         <v>CRQ</v>
       </c>
@@ -1787,27 +1904,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN14" s="1">
+        <v>46193</v>
+      </c>
+      <c r="DO14" s="1">
         <v>46543</v>
       </c>
-      <c r="DO14" t="str">
+      <c r="DP14" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP14" t="str">
+      <c r="DQ14" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ14" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR14" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS14" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT14" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU14" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV14" t="str">
         <v>P-7013</v>
       </c>
     </row>
@@ -1827,9 +1947,15 @@
       <c r="N15" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y15">
+        <v>7014000</v>
+      </c>
       <c r="AM15" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV15" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA15" t="str">
         <v>CRQ</v>
       </c>
@@ -1870,27 +1996,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN15" s="1">
+        <v>46223</v>
+      </c>
+      <c r="DO15" s="1">
         <v>46573</v>
       </c>
-      <c r="DO15" t="str">
+      <c r="DP15" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP15" t="str">
+      <c r="DQ15" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ15" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR15" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS15" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT15" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU15" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV15" t="str">
         <v>P-7014</v>
       </c>
     </row>
@@ -1910,9 +2039,15 @@
       <c r="N16" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y16">
+        <v>7015000</v>
+      </c>
       <c r="AM16" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV16" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA16" t="str">
         <v>Incremental</v>
       </c>
@@ -1950,27 +2085,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN16" s="1">
+        <v>46254</v>
+      </c>
+      <c r="DO16" s="1">
         <v>46604</v>
       </c>
-      <c r="DO16" t="str">
+      <c r="DP16" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP16" t="str">
+      <c r="DQ16" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ16" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR16" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS16" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT16" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU16" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV16" t="str">
         <v>P-7015</v>
       </c>
     </row>
@@ -1990,9 +2128,15 @@
       <c r="N17" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y17">
+        <v>7016000</v>
+      </c>
       <c r="AM17" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV17" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA17" t="str">
         <v>Incremental</v>
       </c>
@@ -2033,27 +2177,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN17" s="1">
+        <v>46285</v>
+      </c>
+      <c r="DO17" s="1">
         <v>46635</v>
       </c>
-      <c r="DO17" t="str">
+      <c r="DP17" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP17" t="str">
+      <c r="DQ17" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ17" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR17" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS17" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT17" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU17" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV17" t="str">
         <v>P-7016</v>
       </c>
     </row>
@@ -2070,9 +2217,15 @@
       <c r="K18" t="str">
         <v>Tanaka, Eli</v>
       </c>
+      <c r="Y18">
+        <v>7017000</v>
+      </c>
       <c r="AM18" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV18" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA18" t="str">
         <v>Incremental</v>
       </c>
@@ -2113,27 +2266,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN18" s="1">
+        <v>46315</v>
+      </c>
+      <c r="DO18" s="1">
         <v>46665</v>
       </c>
-      <c r="DO18" t="str">
+      <c r="DP18" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP18" t="str">
+      <c r="DQ18" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ18" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR18" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS18" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT18" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU18" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV18" t="str">
         <v>P-7017</v>
       </c>
     </row>
@@ -2153,9 +2309,15 @@
       <c r="N19" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y19">
+        <v>7018000</v>
+      </c>
       <c r="AM19" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV19" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA19" t="str">
         <v>Incremental</v>
       </c>
@@ -2196,27 +2358,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN19" s="1">
+        <v>46346</v>
+      </c>
+      <c r="DO19" s="1">
         <v>46696</v>
       </c>
-      <c r="DO19" t="str">
+      <c r="DP19" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP19" t="str">
+      <c r="DQ19" t="str">
         <v>R-007</v>
       </c>
-      <c r="DQ19" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR19" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS19" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT19" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU19" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV19" t="str">
         <v>P-7018</v>
       </c>
     </row>
@@ -2236,9 +2401,15 @@
       <c r="N20" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y20">
+        <v>7019000</v>
+      </c>
       <c r="AM20" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV20" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA20" t="str">
         <v>Incremental</v>
       </c>
@@ -2279,27 +2450,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN20" s="1">
+        <v>46376</v>
+      </c>
+      <c r="DO20" s="1">
         <v>46726</v>
       </c>
-      <c r="DO20" t="str">
+      <c r="DP20" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP20" t="str">
+      <c r="DQ20" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ20" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR20" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS20" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT20" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU20" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV20" t="str">
         <v>P-7019</v>
       </c>
     </row>
@@ -2319,9 +2493,15 @@
       <c r="N21" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y21">
+        <v>7020000</v>
+      </c>
       <c r="AM21" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV21" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA21" t="str">
         <v>Incremental</v>
       </c>
@@ -2362,27 +2542,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN21" s="1">
+        <v>46042</v>
+      </c>
+      <c r="DO21" s="1">
         <v>46392</v>
       </c>
-      <c r="DO21" t="str">
+      <c r="DP21" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP21" t="str">
+      <c r="DQ21" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ21" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR21" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS21" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT21" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU21" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV21" t="str">
         <v>P-7020</v>
       </c>
     </row>
@@ -2402,9 +2585,15 @@
       <c r="N22" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y22">
+        <v>7021000</v>
+      </c>
       <c r="AM22" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV22" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA22" t="str">
         <v>Incremental</v>
       </c>
@@ -2445,27 +2634,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN22" s="1">
+        <v>46073</v>
+      </c>
+      <c r="DO22" s="1">
         <v>46423</v>
       </c>
-      <c r="DO22" t="str">
+      <c r="DP22" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP22" t="str">
+      <c r="DQ22" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ22" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR22" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS22" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT22" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU22" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV22" t="str">
         <v>P-7021</v>
       </c>
     </row>
@@ -2485,9 +2677,15 @@
       <c r="N23" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y23">
+        <v>7022000</v>
+      </c>
       <c r="AM23" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV23" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA23" t="str">
         <v>Incremental</v>
       </c>
@@ -2513,27 +2711,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN23" s="1">
+        <v>46101</v>
+      </c>
+      <c r="DO23" s="1">
         <v>46451</v>
       </c>
-      <c r="DO23" t="str">
+      <c r="DP23" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP23" t="str">
+      <c r="DQ23" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ23" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR23" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS23" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT23" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU23" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV23" t="str">
         <v>P-7022</v>
       </c>
     </row>
@@ -2553,9 +2754,15 @@
       <c r="N24" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y24">
+        <v>7023000</v>
+      </c>
       <c r="AM24" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV24" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA24" t="str">
         <v>Improve</v>
       </c>
@@ -2581,27 +2788,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN24" s="1">
+        <v>46132</v>
+      </c>
+      <c r="DO24" s="1">
         <v>46482</v>
       </c>
-      <c r="DO24" t="str">
+      <c r="DP24" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP24" t="str">
+      <c r="DQ24" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ24" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR24" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS24" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT24" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU24" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV24" t="str">
         <v>P-7023</v>
       </c>
     </row>
@@ -2621,9 +2831,15 @@
       <c r="N25" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y25">
+        <v>7024000</v>
+      </c>
       <c r="AM25" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV25" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA25" t="str">
         <v>Incremental</v>
       </c>
@@ -2664,27 +2880,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN25" s="1">
+        <v>46162</v>
+      </c>
+      <c r="DO25" s="1">
         <v>46512</v>
       </c>
-      <c r="DO25" t="str">
+      <c r="DP25" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP25" t="str">
+      <c r="DQ25" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ25" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR25" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS25" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT25" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU25" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV25" t="str">
         <v>P-7024</v>
       </c>
     </row>
@@ -2704,9 +2923,15 @@
       <c r="N26" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y26">
+        <v>7025000</v>
+      </c>
       <c r="AM26" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV26" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA26" t="str">
         <v>Incremental</v>
       </c>
@@ -2747,27 +2972,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN26" s="1">
+        <v>46193</v>
+      </c>
+      <c r="DO26" s="1">
         <v>46543</v>
       </c>
-      <c r="DO26" t="str">
+      <c r="DP26" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP26" t="str">
+      <c r="DQ26" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ26" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR26" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS26" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT26" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU26" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV26" t="str">
         <v>P-7025</v>
       </c>
     </row>
@@ -2787,9 +3015,15 @@
       <c r="N27" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y27">
+        <v>7026000</v>
+      </c>
       <c r="AM27" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV27" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA27" t="str">
         <v>CRQ</v>
       </c>
@@ -2830,27 +3064,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN27" s="1">
+        <v>46223</v>
+      </c>
+      <c r="DO27" s="1">
         <v>46573</v>
       </c>
-      <c r="DO27" t="str">
+      <c r="DP27" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP27" t="str">
+      <c r="DQ27" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ27" t="str">
+      <c r="DR27" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR27" t="str">
+      <c r="DS27" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS27" t="str">
+      <c r="DT27" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT27" t="str">
+      <c r="DU27" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU27" t="str">
+      <c r="DV27" t="str">
         <v>P-7026</v>
       </c>
     </row>
@@ -2870,9 +3107,15 @@
       <c r="N28" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y28">
+        <v>7027000</v>
+      </c>
       <c r="AM28" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV28" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA28" t="str">
         <v>CRQ</v>
       </c>
@@ -2913,27 +3156,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN28" s="1">
+        <v>46254</v>
+      </c>
+      <c r="DO28" s="1">
         <v>46604</v>
       </c>
-      <c r="DO28" t="str">
+      <c r="DP28" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP28" t="str">
+      <c r="DQ28" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ28" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR28" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS28" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT28" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU28" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV28" t="str">
         <v>P-7027</v>
       </c>
     </row>
@@ -2953,9 +3199,15 @@
       <c r="N29" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y29">
+        <v>7028000</v>
+      </c>
       <c r="AM29" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV29" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA29" t="str">
         <v>Incremental</v>
       </c>
@@ -2996,27 +3248,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN29" s="1">
+        <v>46285</v>
+      </c>
+      <c r="DO29" s="1">
         <v>46635</v>
       </c>
-      <c r="DO29" t="str">
+      <c r="DP29" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP29" t="str">
+      <c r="DQ29" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ29" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR29" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS29" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT29" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU29" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV29" t="str">
         <v>P-7028</v>
       </c>
     </row>
@@ -3036,9 +3291,15 @@
       <c r="N30" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y30">
+        <v>7029000</v>
+      </c>
       <c r="AM30" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV30" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA30" t="str">
         <v>Incremental</v>
       </c>
@@ -3079,27 +3340,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN30" s="1">
+        <v>46315</v>
+      </c>
+      <c r="DO30" s="1">
         <v>46665</v>
       </c>
-      <c r="DO30" t="str">
+      <c r="DP30" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP30" t="str">
+      <c r="DQ30" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ30" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR30" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS30" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT30" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU30" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV30" t="str">
         <v>P-7029</v>
       </c>
     </row>
@@ -3119,9 +3383,15 @@
       <c r="N31" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y31">
+        <v>7030000</v>
+      </c>
       <c r="AM31" t="str">
         <v>On Hold</v>
       </c>
+      <c r="AV31" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA31" t="str">
         <v>Incremental</v>
       </c>
@@ -3162,27 +3432,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN31" s="1">
+        <v>46346</v>
+      </c>
+      <c r="DO31" s="1">
         <v>46696</v>
       </c>
-      <c r="DO31" t="str">
+      <c r="DP31" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP31" t="str">
+      <c r="DQ31" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ31" t="str">
+      <c r="DR31" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR31" t="str">
+      <c r="DS31" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS31" t="str">
+      <c r="DT31" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT31" t="str">
+      <c r="DU31" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU31" t="str">
+      <c r="DV31" t="str">
         <v>P-7030</v>
       </c>
     </row>
@@ -3202,9 +3475,15 @@
       <c r="N32" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y32">
+        <v>7031000</v>
+      </c>
       <c r="AM32" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV32" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA32" t="str">
         <v>Incremental</v>
       </c>
@@ -3245,27 +3524,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN32" s="1">
+        <v>46376</v>
+      </c>
+      <c r="DO32" s="1">
         <v>46726</v>
       </c>
-      <c r="DO32" t="str">
+      <c r="DP32" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP32" t="str">
+      <c r="DQ32" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ32" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR32" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS32" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT32" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU32" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV32" t="str">
         <v>P-7031</v>
       </c>
     </row>
@@ -3285,9 +3567,15 @@
       <c r="N33" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y33">
+        <v>7032000</v>
+      </c>
       <c r="AM33" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV33" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA33" t="str">
         <v>Incremental</v>
       </c>
@@ -3328,27 +3616,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN33" s="1">
+        <v>46042</v>
+      </c>
+      <c r="DO33" s="1">
         <v>46392</v>
       </c>
-      <c r="DO33" t="str">
+      <c r="DP33" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP33" t="str">
+      <c r="DQ33" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ33" t="str">
+      <c r="DR33" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR33" t="str">
+      <c r="DS33" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS33" t="str">
+      <c r="DT33" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT33" t="str">
+      <c r="DU33" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU33" t="str">
+      <c r="DV33" t="str">
         <v>P-7032</v>
       </c>
     </row>
@@ -3368,9 +3659,15 @@
       <c r="N34" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y34">
+        <v>7033000</v>
+      </c>
       <c r="AM34" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV34" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA34" t="str">
         <v>Improve</v>
       </c>
@@ -3405,27 +3702,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN34" s="1">
+        <v>46073</v>
+      </c>
+      <c r="DO34" s="1">
         <v>46423</v>
       </c>
-      <c r="DO34" t="str">
+      <c r="DP34" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP34" t="str">
+      <c r="DQ34" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ34" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR34" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS34" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT34" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU34" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV34" t="str">
         <v>P-7033</v>
       </c>
     </row>
@@ -3445,9 +3745,15 @@
       <c r="N35" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y35">
+        <v>7034000</v>
+      </c>
       <c r="AM35" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV35" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA35" t="str">
         <v>Improve</v>
       </c>
@@ -3482,27 +3788,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN35" s="1">
+        <v>46101</v>
+      </c>
+      <c r="DO35" s="1">
         <v>46451</v>
       </c>
-      <c r="DO35" t="str">
+      <c r="DP35" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP35" t="str">
+      <c r="DQ35" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ35" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR35" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS35" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT35" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU35" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV35" t="str">
         <v>P-7034</v>
       </c>
     </row>
@@ -3522,9 +3831,15 @@
       <c r="N36" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y36">
+        <v>7035000</v>
+      </c>
       <c r="AM36" t="str">
         <v>On Hold</v>
       </c>
+      <c r="AV36" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA36" t="str">
         <v>Incremental</v>
       </c>
@@ -3565,27 +3880,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN36" s="1">
+        <v>46132</v>
+      </c>
+      <c r="DO36" s="1">
         <v>46482</v>
       </c>
-      <c r="DO36" t="str">
+      <c r="DP36" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP36" t="str">
+      <c r="DQ36" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ36" t="str">
+      <c r="DR36" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR36" t="str">
+      <c r="DS36" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS36" t="str">
+      <c r="DT36" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT36" t="str">
+      <c r="DU36" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU36" t="str">
+      <c r="DV36" t="str">
         <v>P-7035</v>
       </c>
     </row>
@@ -3605,9 +3923,15 @@
       <c r="N37" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y37">
+        <v>7036000</v>
+      </c>
       <c r="AM37" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV37" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA37" t="str">
         <v>Improve</v>
       </c>
@@ -3642,27 +3966,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN37" s="1">
+        <v>46162</v>
+      </c>
+      <c r="DO37" s="1">
         <v>46512</v>
       </c>
-      <c r="DO37" t="str">
+      <c r="DP37" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP37" t="str">
+      <c r="DQ37" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ37" t="str">
+      <c r="DR37" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR37" t="str">
+      <c r="DS37" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS37" t="str">
+      <c r="DT37" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT37" t="str">
+      <c r="DU37" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU37" t="str">
+      <c r="DV37" t="str">
         <v>P-7036</v>
       </c>
     </row>
@@ -3682,9 +4009,15 @@
       <c r="N38" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y38">
+        <v>7037000</v>
+      </c>
       <c r="AM38" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV38" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA38" t="str">
         <v>Improve</v>
       </c>
@@ -3719,27 +4052,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN38" s="1">
+        <v>46193</v>
+      </c>
+      <c r="DO38" s="1">
         <v>46543</v>
       </c>
-      <c r="DO38" t="str">
+      <c r="DP38" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP38" t="str">
+      <c r="DQ38" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ38" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR38" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS38" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT38" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU38" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV38" t="str">
         <v>P-7037</v>
       </c>
     </row>
@@ -3759,9 +4095,15 @@
       <c r="N39" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y39">
+        <v>7038000</v>
+      </c>
       <c r="AM39" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV39" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA39" t="str">
         <v>Incremental</v>
       </c>
@@ -3802,27 +4144,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN39" s="1">
+        <v>46223</v>
+      </c>
+      <c r="DO39" s="1">
         <v>46573</v>
       </c>
-      <c r="DO39" t="str">
+      <c r="DP39" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP39" t="str">
+      <c r="DQ39" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ39" t="str">
+      <c r="DR39" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR39" t="str">
+      <c r="DS39" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS39" t="str">
+      <c r="DT39" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT39" t="str">
+      <c r="DU39" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU39" t="str">
+      <c r="DV39" t="str">
         <v>P-7038</v>
       </c>
     </row>
@@ -3842,9 +4187,15 @@
       <c r="N40" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y40">
+        <v>7039000</v>
+      </c>
       <c r="AM40" t="str">
         <v>On Hold</v>
       </c>
+      <c r="AV40" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA40" t="str">
         <v>Incremental</v>
       </c>
@@ -3885,27 +4236,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN40" s="1">
+        <v>46254</v>
+      </c>
+      <c r="DO40" s="1">
         <v>46604</v>
       </c>
-      <c r="DO40" t="str">
+      <c r="DP40" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP40" t="str">
+      <c r="DQ40" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ40" t="str">
+      <c r="DR40" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DR40" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DS40" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DT40" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DT40" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DU40" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV40" t="str">
         <v>P-7039</v>
       </c>
     </row>
@@ -3925,9 +4279,15 @@
       <c r="N41" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y41">
+        <v>7040000</v>
+      </c>
       <c r="AM41" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV41" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA41" t="str">
         <v>Incremental</v>
       </c>
@@ -3968,27 +4328,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN41" s="1">
+        <v>46285</v>
+      </c>
+      <c r="DO41" s="1">
         <v>46635</v>
       </c>
-      <c r="DO41" t="str">
+      <c r="DP41" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP41" t="str">
+      <c r="DQ41" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ41" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR41" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS41" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT41" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU41" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV41" t="str">
         <v>P-7040</v>
       </c>
     </row>
@@ -4008,9 +4371,15 @@
       <c r="N42" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y42">
+        <v>7041000</v>
+      </c>
       <c r="AM42" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV42" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA42" t="str">
         <v>Incremental</v>
       </c>
@@ -4051,27 +4420,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN42" s="1">
+        <v>46315</v>
+      </c>
+      <c r="DO42" s="1">
         <v>46665</v>
       </c>
-      <c r="DO42" t="str">
+      <c r="DP42" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP42" t="str">
+      <c r="DQ42" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ42" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR42" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS42" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT42" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU42" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV42" t="str">
         <v>P-7041</v>
       </c>
     </row>
@@ -4091,9 +4463,15 @@
       <c r="N43" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y43">
+        <v>7042000</v>
+      </c>
       <c r="AM43" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV43" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA43" t="str">
         <v>Improve</v>
       </c>
@@ -4128,27 +4506,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN43" s="1">
+        <v>46346</v>
+      </c>
+      <c r="DO43" s="1">
         <v>46696</v>
       </c>
-      <c r="DO43" t="str">
+      <c r="DP43" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP43" t="str">
+      <c r="DQ43" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ43" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR43" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS43" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT43" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU43" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV43" t="str">
         <v>P-7042</v>
       </c>
     </row>
@@ -4168,9 +4549,15 @@
       <c r="N44" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y44">
+        <v>7043000</v>
+      </c>
       <c r="AM44" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV44" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA44" t="str">
         <v>Improve</v>
       </c>
@@ -4205,27 +4592,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN44" s="1">
+        <v>46376</v>
+      </c>
+      <c r="DO44" s="1">
         <v>46726</v>
       </c>
-      <c r="DO44" t="str">
+      <c r="DP44" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP44" t="str">
+      <c r="DQ44" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ44" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR44" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS44" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT44" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU44" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV44" t="str">
         <v>P-7043</v>
       </c>
     </row>
@@ -4245,9 +4635,15 @@
       <c r="N45" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y45">
+        <v>7044000</v>
+      </c>
       <c r="AM45" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV45" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA45" t="str">
         <v>Incremental</v>
       </c>
@@ -4288,27 +4684,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN45" s="1">
+        <v>46042</v>
+      </c>
+      <c r="DO45" s="1">
         <v>46392</v>
       </c>
-      <c r="DO45" t="str">
+      <c r="DP45" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP45" t="str">
+      <c r="DQ45" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ45" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR45" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS45" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT45" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU45" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV45" t="str">
         <v>P-7044</v>
       </c>
     </row>
@@ -4328,9 +4727,15 @@
       <c r="N46" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y46">
+        <v>7045000</v>
+      </c>
       <c r="AM46" t="str">
         <v>On Hold</v>
       </c>
+      <c r="AV46" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA46" t="str">
         <v>Incremental</v>
       </c>
@@ -4371,27 +4776,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN46" s="1">
+        <v>46073</v>
+      </c>
+      <c r="DO46" s="1">
         <v>46423</v>
       </c>
-      <c r="DO46" t="str">
+      <c r="DP46" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP46" t="str">
+      <c r="DQ46" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ46" t="str">
+      <c r="DR46" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DR46" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DS46" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DT46" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DT46" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DU46" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV46" t="str">
         <v>P-7045</v>
       </c>
     </row>
@@ -4411,9 +4819,15 @@
       <c r="N47" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y47">
+        <v>7046000</v>
+      </c>
       <c r="AM47" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV47" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA47" t="str">
         <v>Incremental</v>
       </c>
@@ -4454,27 +4868,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN47" s="1">
+        <v>46101</v>
+      </c>
+      <c r="DO47" s="1">
         <v>46451</v>
       </c>
-      <c r="DO47" t="str">
+      <c r="DP47" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP47" t="str">
+      <c r="DQ47" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ47" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR47" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS47" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT47" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU47" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV47" t="str">
         <v>P-7046</v>
       </c>
     </row>
@@ -4494,9 +4911,15 @@
       <c r="N48" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y48">
+        <v>7047000</v>
+      </c>
       <c r="AM48" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV48" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA48" t="str">
         <v>CRQ</v>
       </c>
@@ -4537,27 +4960,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN48" s="1">
+        <v>46132</v>
+      </c>
+      <c r="DO48" s="1">
         <v>46482</v>
       </c>
-      <c r="DO48" t="str">
+      <c r="DP48" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP48" t="str">
+      <c r="DQ48" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ48" t="str">
+      <c r="DR48" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DR48" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DS48" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DT48" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DT48" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DU48" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV48" t="str">
         <v>P-7047</v>
       </c>
     </row>
@@ -4577,9 +5003,15 @@
       <c r="N49" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y49">
+        <v>7048000</v>
+      </c>
       <c r="AM49" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV49" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA49" t="str">
         <v>CRQ</v>
       </c>
@@ -4620,27 +5052,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN49" s="1">
+        <v>46162</v>
+      </c>
+      <c r="DO49" s="1">
         <v>46512</v>
       </c>
-      <c r="DO49" t="str">
+      <c r="DP49" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP49" t="str">
+      <c r="DQ49" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ49" t="str">
+      <c r="DR49" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR49" t="str">
+      <c r="DS49" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS49" t="str">
+      <c r="DT49" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT49" t="str">
+      <c r="DU49" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU49" t="str">
+      <c r="DV49" t="str">
         <v>P-7048</v>
       </c>
     </row>
@@ -4660,9 +5095,15 @@
       <c r="N50" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y50">
+        <v>7049000</v>
+      </c>
       <c r="AM50" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV50" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA50" t="str">
         <v>Improve</v>
       </c>
@@ -4697,27 +5138,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN50" s="1">
+        <v>46193</v>
+      </c>
+      <c r="DO50" s="1">
         <v>46543</v>
       </c>
-      <c r="DO50" t="str">
+      <c r="DP50" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP50" t="str">
+      <c r="DQ50" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ50" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR50" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS50" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT50" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU50" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV50" t="str">
         <v>P-7049</v>
       </c>
     </row>
@@ -4737,9 +5181,15 @@
       <c r="N51" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y51">
+        <v>7050000</v>
+      </c>
       <c r="AM51" t="str">
         <v>On Hold</v>
       </c>
+      <c r="AV51" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA51" t="str">
         <v>Improve</v>
       </c>
@@ -4774,27 +5224,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN51" s="1">
+        <v>46223</v>
+      </c>
+      <c r="DO51" s="1">
         <v>46573</v>
       </c>
-      <c r="DO51" t="str">
+      <c r="DP51" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP51" t="str">
+      <c r="DQ51" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ51" t="str">
+      <c r="DR51" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DR51" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DS51" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DT51" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DT51" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DU51" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV51" t="str">
         <v>P-7050</v>
       </c>
     </row>
@@ -4814,9 +5267,15 @@
       <c r="N52" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y52">
+        <v>7051000</v>
+      </c>
       <c r="AM52" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV52" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA52" t="str">
         <v>CRQ</v>
       </c>
@@ -4857,27 +5316,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN52" s="1">
+        <v>46254</v>
+      </c>
+      <c r="DO52" s="1">
         <v>46604</v>
       </c>
-      <c r="DO52" t="str">
+      <c r="DP52" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP52" t="str">
+      <c r="DQ52" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ52" t="str">
+      <c r="DR52" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR52" t="str">
+      <c r="DS52" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS52" t="str">
+      <c r="DT52" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT52" t="str">
+      <c r="DU52" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU52" t="str">
+      <c r="DV52" t="str">
         <v>P-7051</v>
       </c>
     </row>
@@ -4897,9 +5359,15 @@
       <c r="N53" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y53">
+        <v>7052000</v>
+      </c>
       <c r="AM53" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV53" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA53" t="str">
         <v>Incremental</v>
       </c>
@@ -4940,27 +5408,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN53" s="1">
+        <v>46285</v>
+      </c>
+      <c r="DO53" s="1">
         <v>46635</v>
       </c>
-      <c r="DO53" t="str">
+      <c r="DP53" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP53" t="str">
+      <c r="DQ53" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ53" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR53" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS53" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT53" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU53" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV53" t="str">
         <v>P-7052</v>
       </c>
     </row>
@@ -4980,9 +5451,15 @@
       <c r="N54" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y54">
+        <v>7053000</v>
+      </c>
       <c r="AM54" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV54" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA54" t="str">
         <v>Incremental</v>
       </c>
@@ -5023,27 +5500,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN54" s="1">
+        <v>46315</v>
+      </c>
+      <c r="DO54" s="1">
         <v>46665</v>
       </c>
-      <c r="DO54" t="str">
+      <c r="DP54" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP54" t="str">
+      <c r="DQ54" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ54" t="str">
+      <c r="DR54" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR54" t="str">
+      <c r="DS54" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS54" t="str">
+      <c r="DT54" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT54" t="str">
+      <c r="DU54" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU54" t="str">
+      <c r="DV54" t="str">
         <v>P-7053</v>
       </c>
     </row>
@@ -5063,9 +5543,15 @@
       <c r="N55" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y55">
+        <v>7054000</v>
+      </c>
       <c r="AM55" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV55" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA55" t="str">
         <v>CRQ</v>
       </c>
@@ -5106,27 +5592,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN55" s="1">
+        <v>46346</v>
+      </c>
+      <c r="DO55" s="1">
         <v>46696</v>
       </c>
-      <c r="DO55" t="str">
+      <c r="DP55" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP55" t="str">
+      <c r="DQ55" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ55" t="str">
+      <c r="DR55" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR55" t="str">
+      <c r="DS55" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS55" t="str">
+      <c r="DT55" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT55" t="str">
+      <c r="DU55" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU55" t="str">
+      <c r="DV55" t="str">
         <v>P-7054</v>
       </c>
     </row>
@@ -5146,9 +5635,15 @@
       <c r="N56" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y56">
+        <v>7055000</v>
+      </c>
       <c r="AM56" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV56" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA56" t="str">
         <v>Incremental</v>
       </c>
@@ -5189,27 +5684,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN56" s="1">
+        <v>46376</v>
+      </c>
+      <c r="DO56" s="1">
         <v>46726</v>
       </c>
-      <c r="DO56" t="str">
+      <c r="DP56" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP56" t="str">
+      <c r="DQ56" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ56" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR56" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS56" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT56" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU56" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV56" t="str">
         <v>P-7055</v>
       </c>
     </row>
@@ -5229,9 +5727,15 @@
       <c r="N57" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y57">
+        <v>7056000</v>
+      </c>
       <c r="AM57" t="str">
         <v>On Hold</v>
       </c>
+      <c r="AV57" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA57" t="str">
         <v>Incremental</v>
       </c>
@@ -5272,27 +5776,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN57" s="1">
+        <v>46042</v>
+      </c>
+      <c r="DO57" s="1">
         <v>46392</v>
       </c>
-      <c r="DO57" t="str">
+      <c r="DP57" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP57" t="str">
+      <c r="DQ57" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ57" t="str">
+      <c r="DR57" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR57" t="str">
+      <c r="DS57" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS57" t="str">
+      <c r="DT57" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT57" t="str">
+      <c r="DU57" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU57" t="str">
+      <c r="DV57" t="str">
         <v>P-7056</v>
       </c>
     </row>
@@ -5312,9 +5819,15 @@
       <c r="N58" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y58">
+        <v>7057000</v>
+      </c>
       <c r="AM58" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV58" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA58" t="str">
         <v>CRQ</v>
       </c>
@@ -5355,27 +5868,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN58" s="1">
+        <v>46073</v>
+      </c>
+      <c r="DO58" s="1">
         <v>46423</v>
       </c>
-      <c r="DO58" t="str">
+      <c r="DP58" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP58" t="str">
+      <c r="DQ58" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ58" t="str">
+      <c r="DR58" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DR58" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DS58" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DT58" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DT58" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DU58" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV58" t="str">
         <v>P-7057</v>
       </c>
     </row>
@@ -5395,9 +5911,15 @@
       <c r="N59" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y59">
+        <v>7058000</v>
+      </c>
       <c r="AM59" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV59" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA59" t="str">
         <v>Incremental</v>
       </c>
@@ -5438,27 +5960,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN59" s="1">
+        <v>46101</v>
+      </c>
+      <c r="DO59" s="1">
         <v>46451</v>
       </c>
-      <c r="DO59" t="str">
+      <c r="DP59" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP59" t="str">
+      <c r="DQ59" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ59" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR59" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS59" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT59" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU59" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV59" t="str">
         <v>P-7058</v>
       </c>
     </row>
@@ -5478,9 +6003,15 @@
       <c r="N60" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y60">
+        <v>7059000</v>
+      </c>
       <c r="AM60" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV60" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA60" t="str">
         <v>CRQ</v>
       </c>
@@ -5521,27 +6052,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN60" s="1">
+        <v>46132</v>
+      </c>
+      <c r="DO60" s="1">
         <v>46482</v>
       </c>
-      <c r="DO60" t="str">
+      <c r="DP60" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP60" t="str">
+      <c r="DQ60" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ60" t="str">
+      <c r="DR60" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DR60" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DS60" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DT60" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DT60" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DU60" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV60" t="str">
         <v>P-7059</v>
       </c>
     </row>
@@ -5561,9 +6095,15 @@
       <c r="N61" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y61">
+        <v>7060000</v>
+      </c>
       <c r="AM61" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV61" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA61" t="str">
         <v>Incremental</v>
       </c>
@@ -5604,27 +6144,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN61" s="1">
+        <v>46162</v>
+      </c>
+      <c r="DO61" s="1">
         <v>46512</v>
       </c>
-      <c r="DO61" t="str">
+      <c r="DP61" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP61" t="str">
+      <c r="DQ61" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ61" t="str">
+      <c r="DR61" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR61" t="str">
+      <c r="DS61" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS61" t="str">
+      <c r="DT61" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT61" t="str">
+      <c r="DU61" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU61" t="str">
+      <c r="DV61" t="str">
         <v>P-7060</v>
       </c>
     </row>
@@ -5644,9 +6187,15 @@
       <c r="N62" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y62">
+        <v>7061000</v>
+      </c>
       <c r="AM62" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV62" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA62" t="str">
         <v>Incremental</v>
       </c>
@@ -5687,27 +6236,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN62" s="1">
+        <v>46193</v>
+      </c>
+      <c r="DO62" s="1">
         <v>46543</v>
       </c>
-      <c r="DO62" t="str">
+      <c r="DP62" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP62" t="str">
+      <c r="DQ62" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ62" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR62" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS62" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT62" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU62" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV62" t="str">
         <v>P-7061</v>
       </c>
     </row>
@@ -5727,9 +6279,15 @@
       <c r="N63" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y63">
+        <v>7062000</v>
+      </c>
       <c r="AM63" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV63" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA63" t="str">
         <v>Incremental</v>
       </c>
@@ -5770,27 +6328,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN63" s="1">
+        <v>46223</v>
+      </c>
+      <c r="DO63" s="1">
         <v>46573</v>
       </c>
-      <c r="DO63" t="str">
+      <c r="DP63" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP63" t="str">
+      <c r="DQ63" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ63" t="str">
+      <c r="DR63" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR63" t="str">
+      <c r="DS63" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS63" t="str">
+      <c r="DT63" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT63" t="str">
+      <c r="DU63" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU63" t="str">
+      <c r="DV63" t="str">
         <v>P-7062</v>
       </c>
     </row>
@@ -5810,9 +6371,15 @@
       <c r="N64" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y64">
+        <v>7063000</v>
+      </c>
       <c r="AM64" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV64" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA64" t="str">
         <v>Incremental</v>
       </c>
@@ -5853,27 +6420,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN64" s="1">
+        <v>46254</v>
+      </c>
+      <c r="DO64" s="1">
         <v>46604</v>
       </c>
-      <c r="DO64" t="str">
+      <c r="DP64" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP64" t="str">
+      <c r="DQ64" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ64" t="str">
+      <c r="DR64" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DR64" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DS64" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DT64" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DT64" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DU64" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV64" t="str">
         <v>P-7063</v>
       </c>
     </row>
@@ -5893,9 +6463,15 @@
       <c r="N65" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y65">
+        <v>7064000</v>
+      </c>
       <c r="AM65" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV65" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA65" t="str">
         <v>CRQ</v>
       </c>
@@ -5936,27 +6512,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN65" s="1">
+        <v>46285</v>
+      </c>
+      <c r="DO65" s="1">
         <v>46635</v>
       </c>
-      <c r="DO65" t="str">
+      <c r="DP65" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP65" t="str">
+      <c r="DQ65" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ65" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR65" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS65" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT65" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU65" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV65" t="str">
         <v>P-7064</v>
       </c>
     </row>
@@ -5976,9 +6555,15 @@
       <c r="N66" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y66">
+        <v>7065000</v>
+      </c>
       <c r="AM66" t="str">
         <v>On Hold</v>
       </c>
+      <c r="AV66" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA66" t="str">
         <v>Incremental</v>
       </c>
@@ -6019,27 +6604,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN66" s="1">
+        <v>46315</v>
+      </c>
+      <c r="DO66" s="1">
         <v>46665</v>
       </c>
-      <c r="DO66" t="str">
+      <c r="DP66" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP66" t="str">
+      <c r="DQ66" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ66" t="str">
+      <c r="DR66" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR66" t="str">
+      <c r="DS66" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS66" t="str">
+      <c r="DT66" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT66" t="str">
+      <c r="DU66" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU66" t="str">
+      <c r="DV66" t="str">
         <v>P-7065</v>
       </c>
     </row>
@@ -6059,9 +6647,15 @@
       <c r="N67" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y67">
+        <v>7066000</v>
+      </c>
       <c r="AM67" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV67" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA67" t="str">
         <v>Incremental</v>
       </c>
@@ -6102,27 +6696,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN67" s="1">
+        <v>46346</v>
+      </c>
+      <c r="DO67" s="1">
         <v>46696</v>
       </c>
-      <c r="DO67" t="str">
+      <c r="DP67" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP67" t="str">
+      <c r="DQ67" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ67" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR67" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS67" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT67" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU67" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV67" t="str">
         <v>P-7066</v>
       </c>
     </row>
@@ -6142,9 +6739,15 @@
       <c r="N68" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y68">
+        <v>7067000</v>
+      </c>
       <c r="AM68" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV68" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA68" t="str">
         <v>CRQ</v>
       </c>
@@ -6185,27 +6788,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN68" s="1">
+        <v>46376</v>
+      </c>
+      <c r="DO68" s="1">
         <v>46726</v>
       </c>
-      <c r="DO68" t="str">
+      <c r="DP68" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP68" t="str">
+      <c r="DQ68" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ68" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR68" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS68" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT68" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU68" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV68" t="str">
         <v>P-7067</v>
       </c>
     </row>
@@ -6225,9 +6831,15 @@
       <c r="N69" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y69">
+        <v>7068000</v>
+      </c>
       <c r="AM69" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV69" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA69" t="str">
         <v>CRQ</v>
       </c>
@@ -6268,27 +6880,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN69" s="1">
+        <v>46042</v>
+      </c>
+      <c r="DO69" s="1">
         <v>46392</v>
       </c>
-      <c r="DO69" t="str">
+      <c r="DP69" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP69" t="str">
+      <c r="DQ69" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ69" t="str">
+      <c r="DR69" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR69" t="str">
+      <c r="DS69" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS69" t="str">
+      <c r="DT69" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT69" t="str">
+      <c r="DU69" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU69" t="str">
+      <c r="DV69" t="str">
         <v>P-7068</v>
       </c>
     </row>
@@ -6308,9 +6923,15 @@
       <c r="N70" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y70">
+        <v>7069000</v>
+      </c>
       <c r="AM70" t="str">
         <v>On Hold</v>
       </c>
+      <c r="AV70" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA70" t="str">
         <v>Incremental</v>
       </c>
@@ -6351,27 +6972,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN70" s="1">
+        <v>46073</v>
+      </c>
+      <c r="DO70" s="1">
         <v>46423</v>
       </c>
-      <c r="DO70" t="str">
+      <c r="DP70" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP70" t="str">
+      <c r="DQ70" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ70" t="str">
+      <c r="DR70" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR70" t="str">
+      <c r="DS70" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS70" t="str">
+      <c r="DT70" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT70" t="str">
+      <c r="DU70" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU70" t="str">
+      <c r="DV70" t="str">
         <v>P-7069</v>
       </c>
     </row>
@@ -6391,9 +7015,15 @@
       <c r="N71" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y71">
+        <v>7070000</v>
+      </c>
       <c r="AM71" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV71" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA71" t="str">
         <v>Incremental</v>
       </c>
@@ -6434,27 +7064,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN71" s="1">
+        <v>46101</v>
+      </c>
+      <c r="DO71" s="1">
         <v>46451</v>
       </c>
-      <c r="DO71" t="str">
+      <c r="DP71" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP71" t="str">
+      <c r="DQ71" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ71" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR71" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS71" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT71" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU71" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV71" t="str">
         <v>P-7070</v>
       </c>
     </row>
@@ -6474,9 +7107,15 @@
       <c r="N72" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y72">
+        <v>7071000</v>
+      </c>
       <c r="AM72" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV72" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA72" t="str">
         <v>Improve</v>
       </c>
@@ -6511,27 +7150,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN72" s="1">
+        <v>46132</v>
+      </c>
+      <c r="DO72" s="1">
         <v>46482</v>
       </c>
-      <c r="DO72" t="str">
+      <c r="DP72" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP72" t="str">
+      <c r="DQ72" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ72" t="str">
+      <c r="DR72" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DR72" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DS72" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DT72" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DT72" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DU72" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV72" t="str">
         <v>P-7071</v>
       </c>
     </row>
@@ -6551,9 +7193,15 @@
       <c r="N73" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y73">
+        <v>7072000</v>
+      </c>
       <c r="AM73" t="str">
         <v>On Hold</v>
       </c>
+      <c r="AV73" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA73" t="str">
         <v>Incremental</v>
       </c>
@@ -6594,27 +7242,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN73" s="1">
+        <v>46162</v>
+      </c>
+      <c r="DO73" s="1">
         <v>46512</v>
       </c>
-      <c r="DO73" t="str">
+      <c r="DP73" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP73" t="str">
+      <c r="DQ73" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ73" t="str">
+      <c r="DR73" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR73" t="str">
+      <c r="DS73" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS73" t="str">
+      <c r="DT73" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT73" t="str">
+      <c r="DU73" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU73" t="str">
+      <c r="DV73" t="str">
         <v>P-7072</v>
       </c>
     </row>
@@ -6634,9 +7285,15 @@
       <c r="N74" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y74">
+        <v>7073000</v>
+      </c>
       <c r="AM74" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV74" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA74" t="str">
         <v>CRQ</v>
       </c>
@@ -6677,27 +7334,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN74" s="1">
+        <v>46193</v>
+      </c>
+      <c r="DO74" s="1">
         <v>46543</v>
       </c>
-      <c r="DO74" t="str">
+      <c r="DP74" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP74" t="str">
+      <c r="DQ74" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ74" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR74" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS74" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT74" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU74" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV74" t="str">
         <v>P-7073</v>
       </c>
     </row>
@@ -6717,9 +7377,15 @@
       <c r="N75" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y75">
+        <v>7074000</v>
+      </c>
       <c r="AM75" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV75" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA75" t="str">
         <v>CRQ</v>
       </c>
@@ -6760,27 +7426,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN75" s="1">
+        <v>46223</v>
+      </c>
+      <c r="DO75" s="1">
         <v>46573</v>
       </c>
-      <c r="DO75" t="str">
+      <c r="DP75" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP75" t="str">
+      <c r="DQ75" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ75" t="str">
+      <c r="DR75" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR75" t="str">
+      <c r="DS75" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS75" t="str">
+      <c r="DT75" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT75" t="str">
+      <c r="DU75" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU75" t="str">
+      <c r="DV75" t="str">
         <v>P-7074</v>
       </c>
     </row>
@@ -6800,9 +7469,15 @@
       <c r="N76" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y76">
+        <v>7075000</v>
+      </c>
       <c r="AM76" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV76" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA76" t="str">
         <v>Improve</v>
       </c>
@@ -6837,27 +7512,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN76" s="1">
+        <v>46254</v>
+      </c>
+      <c r="DO76" s="1">
         <v>46604</v>
       </c>
-      <c r="DO76" t="str">
+      <c r="DP76" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP76" t="str">
+      <c r="DQ76" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ76" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR76" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS76" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT76" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU76" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV76" t="str">
         <v>P-7075</v>
       </c>
     </row>
@@ -6877,9 +7555,15 @@
       <c r="N77" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y77">
+        <v>7076000</v>
+      </c>
       <c r="AM77" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV77" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA77" t="str">
         <v>Incremental</v>
       </c>
@@ -6920,27 +7604,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN77" s="1">
+        <v>46285</v>
+      </c>
+      <c r="DO77" s="1">
         <v>46635</v>
       </c>
-      <c r="DO77" t="str">
+      <c r="DP77" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP77" t="str">
+      <c r="DQ77" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ77" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR77" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS77" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT77" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU77" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV77" t="str">
         <v>P-7076</v>
       </c>
     </row>
@@ -6960,9 +7647,15 @@
       <c r="N78" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y78">
+        <v>7077000</v>
+      </c>
       <c r="AM78" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV78" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA78" t="str">
         <v>Improve</v>
       </c>
@@ -6997,27 +7690,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN78" s="1">
+        <v>46315</v>
+      </c>
+      <c r="DO78" s="1">
         <v>46665</v>
       </c>
-      <c r="DO78" t="str">
+      <c r="DP78" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP78" t="str">
+      <c r="DQ78" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ78" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR78" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS78" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT78" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU78" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV78" t="str">
         <v>P-7077</v>
       </c>
     </row>
@@ -7037,9 +7733,15 @@
       <c r="N79" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y79">
+        <v>7078000</v>
+      </c>
       <c r="AM79" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV79" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA79" t="str">
         <v>CRQ</v>
       </c>
@@ -7080,27 +7782,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN79" s="1">
+        <v>46346</v>
+      </c>
+      <c r="DO79" s="1">
         <v>46696</v>
       </c>
-      <c r="DO79" t="str">
+      <c r="DP79" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP79" t="str">
+      <c r="DQ79" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ79" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR79" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS79" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT79" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU79" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV79" t="str">
         <v>P-7078</v>
       </c>
     </row>
@@ -7120,9 +7825,15 @@
       <c r="N80" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y80">
+        <v>7079000</v>
+      </c>
       <c r="AM80" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV80" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA80" t="str">
         <v>Incremental</v>
       </c>
@@ -7163,27 +7874,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN80" s="1">
+        <v>46376</v>
+      </c>
+      <c r="DO80" s="1">
         <v>46726</v>
       </c>
-      <c r="DO80" t="str">
+      <c r="DP80" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP80" t="str">
+      <c r="DQ80" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ80" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR80" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS80" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT80" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU80" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV80" t="str">
         <v>P-7079</v>
       </c>
     </row>
@@ -7203,9 +7917,15 @@
       <c r="N81" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y81">
+        <v>7080000</v>
+      </c>
       <c r="AM81" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV81" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA81" t="str">
         <v>Incremental</v>
       </c>
@@ -7246,27 +7966,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN81" s="1">
+        <v>46042</v>
+      </c>
+      <c r="DO81" s="1">
         <v>46392</v>
       </c>
-      <c r="DO81" t="str">
+      <c r="DP81" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP81" t="str">
+      <c r="DQ81" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ81" t="str">
+      <c r="DR81" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DR81" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DS81" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DT81" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DT81" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DU81" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV81" t="str">
         <v>P-7080</v>
       </c>
     </row>
@@ -7286,9 +8009,15 @@
       <c r="N82" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y82">
+        <v>7081000</v>
+      </c>
       <c r="AM82" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV82" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA82" t="str">
         <v>Incremental</v>
       </c>
@@ -7329,27 +8058,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN82" s="1">
+        <v>46073</v>
+      </c>
+      <c r="DO82" s="1">
         <v>46423</v>
       </c>
-      <c r="DO82" t="str">
+      <c r="DP82" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP82" t="str">
+      <c r="DQ82" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ82" t="str">
+      <c r="DR82" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR82" t="str">
+      <c r="DS82" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS82" t="str">
+      <c r="DT82" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT82" t="str">
+      <c r="DU82" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU82" t="str">
+      <c r="DV82" t="str">
         <v>P-7081</v>
       </c>
     </row>
@@ -7369,9 +8101,15 @@
       <c r="N83" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y83">
+        <v>7082000</v>
+      </c>
       <c r="AM83" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV83" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA83" t="str">
         <v>Improve</v>
       </c>
@@ -7406,27 +8144,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN83" s="1">
+        <v>46101</v>
+      </c>
+      <c r="DO83" s="1">
         <v>46451</v>
       </c>
-      <c r="DO83" t="str">
+      <c r="DP83" t="str">
         <v>Improvement.On Platform</v>
       </c>
-      <c r="DP83" t="str">
+      <c r="DQ83" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ83" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR83" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS83" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT83" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU83" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV83" t="str">
         <v>P-7082</v>
       </c>
     </row>
@@ -7446,9 +8187,15 @@
       <c r="N84" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y84">
+        <v>7083000</v>
+      </c>
       <c r="AM84" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV84" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA84" t="str">
         <v>Incremental</v>
       </c>
@@ -7489,27 +8236,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN84" s="1">
+        <v>46132</v>
+      </c>
+      <c r="DO84" s="1">
         <v>46482</v>
       </c>
-      <c r="DO84" t="str">
+      <c r="DP84" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP84" t="str">
+      <c r="DQ84" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ84" t="str">
+      <c r="DR84" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR84" t="str">
+      <c r="DS84" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS84" t="str">
+      <c r="DT84" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT84" t="str">
+      <c r="DU84" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU84" t="str">
+      <c r="DV84" t="str">
         <v>P-7083</v>
       </c>
     </row>
@@ -7529,9 +8279,15 @@
       <c r="N85" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y85">
+        <v>7084000</v>
+      </c>
       <c r="AM85" t="str">
         <v>On Hold</v>
       </c>
+      <c r="AV85" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA85" t="str">
         <v>Incremental</v>
       </c>
@@ -7572,27 +8328,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN85" s="1">
+        <v>46162</v>
+      </c>
+      <c r="DO85" s="1">
         <v>46512</v>
       </c>
-      <c r="DO85" t="str">
+      <c r="DP85" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP85" t="str">
+      <c r="DQ85" t="str">
         <v>R-001</v>
       </c>
-      <c r="DQ85" t="str">
+      <c r="DR85" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DR85" t="str">
+      <c r="DS85" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DS85" t="str">
+      <c r="DT85" t="str">
         <v>02 01 Discovery</v>
       </c>
-      <c r="DT85" t="str">
+      <c r="DU85" t="str">
         <v>02 Plan Phase</v>
       </c>
-      <c r="DU85" t="str">
+      <c r="DV85" t="str">
         <v>P-7084</v>
       </c>
     </row>
@@ -7612,9 +8371,15 @@
       <c r="N86" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y86">
+        <v>7085000</v>
+      </c>
       <c r="AM86" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV86" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA86" t="str">
         <v>CRQ</v>
       </c>
@@ -7655,27 +8420,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN86" s="1">
+        <v>46193</v>
+      </c>
+      <c r="DO86" s="1">
         <v>46543</v>
       </c>
-      <c r="DO86" t="str">
+      <c r="DP86" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP86" t="str">
+      <c r="DQ86" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ86" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR86" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS86" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT86" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU86" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV86" t="str">
         <v>P-7085</v>
       </c>
     </row>
@@ -7695,9 +8463,15 @@
       <c r="N87" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y87">
+        <v>7086000</v>
+      </c>
       <c r="AM87" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV87" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA87" t="str">
         <v>CRQ</v>
       </c>
@@ -7738,27 +8512,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN87" s="1">
+        <v>46223</v>
+      </c>
+      <c r="DO87" s="1">
         <v>46573</v>
       </c>
-      <c r="DO87" t="str">
+      <c r="DP87" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP87" t="str">
+      <c r="DQ87" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ87" t="str">
+      <c r="DR87" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR87" t="str">
+      <c r="DS87" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS87" t="str">
+      <c r="DT87" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT87" t="str">
+      <c r="DU87" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU87" t="str">
+      <c r="DV87" t="str">
         <v>P-7086</v>
       </c>
     </row>
@@ -7778,9 +8555,15 @@
       <c r="N88" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y88">
+        <v>7087000</v>
+      </c>
       <c r="AM88" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV88" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA88" t="str">
         <v>Incremental</v>
       </c>
@@ -7821,27 +8604,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN88" s="1">
+        <v>46254</v>
+      </c>
+      <c r="DO88" s="1">
         <v>46604</v>
       </c>
-      <c r="DO88" t="str">
+      <c r="DP88" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP88" t="str">
+      <c r="DQ88" t="str">
         <v>R-004</v>
       </c>
-      <c r="DQ88" t="str">
+      <c r="DR88" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR88" t="str">
+      <c r="DS88" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS88" t="str">
+      <c r="DT88" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT88" t="str">
+      <c r="DU88" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU88" t="str">
+      <c r="DV88" t="str">
         <v>P-7087</v>
       </c>
     </row>
@@ -7861,9 +8647,15 @@
       <c r="N89" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y89">
+        <v>7088000</v>
+      </c>
       <c r="AM89" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV89" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA89" t="str">
         <v>Incremental</v>
       </c>
@@ -7904,27 +8696,30 @@
         <v>Sponsor.Outdoors</v>
       </c>
       <c r="DN89" s="1">
+        <v>46285</v>
+      </c>
+      <c r="DO89" s="1">
         <v>46635</v>
       </c>
-      <c r="DO89" t="str">
+      <c r="DP89" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP89" t="str">
+      <c r="DQ89" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ89" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR89" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS89" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT89" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU89" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV89" t="str">
         <v>P-7088</v>
       </c>
     </row>
@@ -7944,9 +8739,15 @@
       <c r="N90" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y90">
+        <v>7089000</v>
+      </c>
       <c r="AM90" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV90" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA90" t="str">
         <v>Incremental</v>
       </c>
@@ -7987,27 +8788,30 @@
         <v>Sponsor.Water Bath</v>
       </c>
       <c r="DN90" s="1">
+        <v>46315</v>
+      </c>
+      <c r="DO90" s="1">
         <v>46665</v>
       </c>
-      <c r="DO90" t="str">
+      <c r="DP90" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP90" t="str">
+      <c r="DQ90" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ90" t="str">
+      <c r="DR90" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR90" t="str">
+      <c r="DS90" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS90" t="str">
+      <c r="DT90" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT90" t="str">
+      <c r="DU90" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU90" t="str">
+      <c r="DV90" t="str">
         <v>P-7089</v>
       </c>
     </row>
@@ -8027,9 +8831,15 @@
       <c r="N91" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Y91">
+        <v>7090000</v>
+      </c>
       <c r="AM91" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV91" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA91" t="str">
         <v>Incremental</v>
       </c>
@@ -8070,27 +8880,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN91" s="1">
+        <v>46346</v>
+      </c>
+      <c r="DO91" s="1">
         <v>46696</v>
       </c>
-      <c r="DO91" t="str">
+      <c r="DP91" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP91" t="str">
+      <c r="DQ91" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ91" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR91" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS91" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT91" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU91" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV91" t="str">
         <v>P-7090</v>
       </c>
     </row>
@@ -8110,9 +8923,15 @@
       <c r="N92" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y92">
+        <v>7091000</v>
+      </c>
       <c r="AM92" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV92" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA92" t="str">
         <v>Incremental</v>
       </c>
@@ -8153,27 +8972,30 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN92" s="1">
+        <v>46376</v>
+      </c>
+      <c r="DO92" s="1">
         <v>46726</v>
       </c>
-      <c r="DO92" t="str">
+      <c r="DP92" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP92" t="str">
+      <c r="DQ92" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ92" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR92" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS92" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT92" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU92" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV92" t="str">
         <v>P-7091</v>
       </c>
     </row>
@@ -8193,9 +9015,15 @@
       <c r="N93" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Y93">
+        <v>7092000</v>
+      </c>
       <c r="AM93" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV93" t="str">
+        <v>Green</v>
+      </c>
       <c r="BA93" t="str">
         <v>CRQ</v>
       </c>
@@ -8236,27 +9064,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN93" s="1">
+        <v>46042</v>
+      </c>
+      <c r="DO93" s="1">
         <v>46392</v>
       </c>
-      <c r="DO93" t="str">
+      <c r="DP93" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP93" t="str">
+      <c r="DQ93" t="str">
         <v>R-002</v>
       </c>
-      <c r="DQ93" t="str">
+      <c r="DR93" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DR93" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DS93" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DT93" t="str">
         <v>03 03 Develop</v>
       </c>
-      <c r="DT93" t="str">
-        <v>03 Active Phase</v>
-      </c>
       <c r="DU93" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV93" t="str">
         <v>P-7092</v>
       </c>
     </row>
@@ -8276,9 +9107,15 @@
       <c r="N94" t="str">
         <v>Beta</v>
       </c>
+      <c r="Y94">
+        <v>7093000</v>
+      </c>
       <c r="AM94" t="str">
         <v>Completed</v>
       </c>
+      <c r="AV94" t="str">
+        <v>Yellow</v>
+      </c>
       <c r="BA94" t="str">
         <v>CRQ</v>
       </c>
@@ -8319,27 +9156,30 @@
         <v>Sponsor.Security</v>
       </c>
       <c r="DN94" s="1">
+        <v>46073</v>
+      </c>
+      <c r="DO94" s="1">
         <v>46423</v>
       </c>
-      <c r="DO94" t="str">
+      <c r="DP94" t="str">
         <v>Compliance.On Platform</v>
       </c>
-      <c r="DP94" t="str">
+      <c r="DQ94" t="str">
         <v>R-003</v>
       </c>
-      <c r="DQ94" t="str">
+      <c r="DR94" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DR94" t="str">
+      <c r="DS94" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DS94" t="str">
+      <c r="DT94" t="str">
         <v>04 01 Launch</v>
       </c>
-      <c r="DT94" t="str">
+      <c r="DU94" t="str">
         <v>04 Launch Phase</v>
       </c>
-      <c r="DU94" t="str">
+      <c r="DV94" t="str">
         <v>P-7093</v>
       </c>
     </row>
@@ -8359,9 +9199,15 @@
       <c r="N95" t="str">
         <v>Delta</v>
       </c>
+      <c r="Y95">
+        <v>7094000</v>
+      </c>
       <c r="AM95" t="str">
         <v>In Progress</v>
       </c>
+      <c r="AV95" t="str">
+        <v>Red</v>
+      </c>
       <c r="BA95" t="str">
         <v>Incremental</v>
       </c>
@@ -8402,33 +9248,36 @@
         <v>Sponsor.Water Kitchen</v>
       </c>
       <c r="DN95" s="1">
+        <v>46101</v>
+      </c>
+      <c r="DO95" s="1">
         <v>46451</v>
       </c>
-      <c r="DO95" t="str">
+      <c r="DP95" t="str">
         <v>Product Expansion/Refresh.On Platform</v>
       </c>
-      <c r="DP95" t="str">
+      <c r="DQ95" t="str">
         <v>R-005</v>
       </c>
-      <c r="DQ95" t="str">
-        <v>03 02 Converge</v>
-      </c>
       <c r="DR95" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DS95" t="str">
-        <v>03 02 Converge</v>
+        <v>03 Active Phase</v>
       </c>
       <c r="DT95" t="str">
-        <v>03 Active Phase</v>
+        <v>03 02 Converge</v>
       </c>
       <c r="DU95" t="str">
+        <v>03 Active Phase</v>
+      </c>
+      <c r="DV95" t="str">
         <v>P-7094</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:DU95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:DV95"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/fixtures/dq-project-fixture.xlsx
+++ b/tests/fixtures/dq-project-fixture.xlsx
@@ -796,6 +796,9 @@
       <c r="N2" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q2" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y2">
         <v>7001000</v>
       </c>
@@ -849,9 +852,6 @@
       </c>
       <c r="DO2" s="1">
         <v>46543</v>
-      </c>
-      <c r="DP2" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ2" t="str">
         <v>R-004</v>
@@ -888,6 +888,9 @@
       <c r="N3" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q3" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y3">
         <v>7002000</v>
       </c>
@@ -941,9 +944,6 @@
       </c>
       <c r="DO3" s="1">
         <v>46573</v>
-      </c>
-      <c r="DP3" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ3" t="str">
         <v>R-002</v>
@@ -980,6 +980,9 @@
       <c r="N4" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q4" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y4">
         <v>7003000</v>
       </c>
@@ -1033,9 +1036,6 @@
       </c>
       <c r="DO4" s="1">
         <v>46604</v>
-      </c>
-      <c r="DP4" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ4" t="str">
         <v>R-004</v>
@@ -1072,6 +1072,9 @@
       <c r="N5" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q5" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y5">
         <v>7004000</v>
       </c>
@@ -1125,9 +1128,6 @@
       </c>
       <c r="DO5" s="1">
         <v>46635</v>
-      </c>
-      <c r="DP5" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ5" t="str">
         <v>R-003</v>
@@ -1164,6 +1164,9 @@
       <c r="N6" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q6" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y6">
         <v>7005000</v>
       </c>
@@ -1214,9 +1217,6 @@
       </c>
       <c r="DO6" s="1">
         <v>46665</v>
-      </c>
-      <c r="DP6" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ6" t="str">
         <v>R-002</v>
@@ -1253,6 +1253,9 @@
       <c r="N7" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q7" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y7">
         <v>7006000</v>
       </c>
@@ -1303,9 +1306,6 @@
       </c>
       <c r="DO7" s="1">
         <v>46696</v>
-      </c>
-      <c r="DP7" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ7" t="str">
         <v>R-005</v>
@@ -1342,6 +1342,9 @@
       <c r="N8" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q8" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y8">
         <v>7007000</v>
       </c>
@@ -1395,9 +1398,6 @@
       </c>
       <c r="DO8" s="1">
         <v>46726</v>
-      </c>
-      <c r="DP8" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ8" t="str">
         <v>R-001</v>
@@ -1434,6 +1434,9 @@
       <c r="N9" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q9" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y9">
         <v>7008000</v>
       </c>
@@ -1472,9 +1475,6 @@
       </c>
       <c r="DO9" s="1">
         <v>46392</v>
-      </c>
-      <c r="DP9" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ9" t="str">
         <v>R-004</v>
@@ -1511,6 +1511,9 @@
       <c r="N10" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q10" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y10">
         <v>7009000</v>
       </c>
@@ -1555,9 +1558,6 @@
       </c>
       <c r="DO10" s="1">
         <v>46423</v>
-      </c>
-      <c r="DP10" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ10" t="str">
         <v>R-002</v>
@@ -1594,6 +1594,9 @@
       <c r="N11" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q11" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y11">
         <v>7010000</v>
       </c>
@@ -1641,9 +1644,6 @@
       </c>
       <c r="DO11" s="1">
         <v>46451</v>
-      </c>
-      <c r="DP11" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ11" t="str">
         <v>R-004</v>
@@ -1680,6 +1680,9 @@
       <c r="N12" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q12" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y12">
         <v>7011000</v>
       </c>
@@ -1727,9 +1730,6 @@
       </c>
       <c r="DO12" s="1">
         <v>46482</v>
-      </c>
-      <c r="DP12" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ12" t="str">
         <v>R-004</v>
@@ -1766,6 +1766,9 @@
       <c r="N13" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q13" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y13">
         <v>7012000</v>
       </c>
@@ -1816,9 +1819,6 @@
       </c>
       <c r="DO13" s="1">
         <v>46512</v>
-      </c>
-      <c r="DP13" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ13" t="str">
         <v>R-001</v>
@@ -1855,6 +1855,9 @@
       <c r="N14" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q14" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y14">
         <v>7013000</v>
       </c>
@@ -1908,9 +1911,6 @@
       </c>
       <c r="DO14" s="1">
         <v>46543</v>
-      </c>
-      <c r="DP14" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ14" t="str">
         <v>R-005</v>
@@ -1947,6 +1947,9 @@
       <c r="N15" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q15" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y15">
         <v>7014000</v>
       </c>
@@ -2000,9 +2003,6 @@
       </c>
       <c r="DO15" s="1">
         <v>46573</v>
-      </c>
-      <c r="DP15" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ15" t="str">
         <v>R-001</v>
@@ -2039,6 +2039,9 @@
       <c r="N16" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q16" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y16">
         <v>7015000</v>
       </c>
@@ -2089,9 +2092,6 @@
       </c>
       <c r="DO16" s="1">
         <v>46604</v>
-      </c>
-      <c r="DP16" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ16" t="str">
         <v>R-005</v>
@@ -2128,6 +2128,9 @@
       <c r="N17" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q17" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y17">
         <v>7016000</v>
       </c>
@@ -2181,9 +2184,6 @@
       </c>
       <c r="DO17" s="1">
         <v>46635</v>
-      </c>
-      <c r="DP17" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ17" t="str">
         <v>R-004</v>
@@ -2217,6 +2217,9 @@
       <c r="K18" t="str">
         <v>Tanaka, Eli</v>
       </c>
+      <c r="Q18" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y18">
         <v>7017000</v>
       </c>
@@ -2270,9 +2273,6 @@
       </c>
       <c r="DO18" s="1">
         <v>46665</v>
-      </c>
-      <c r="DP18" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ18" t="str">
         <v>R-005</v>
@@ -2309,6 +2309,9 @@
       <c r="N19" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q19" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y19">
         <v>7018000</v>
       </c>
@@ -2362,9 +2365,6 @@
       </c>
       <c r="DO19" s="1">
         <v>46696</v>
-      </c>
-      <c r="DP19" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ19" t="str">
         <v>R-007</v>
@@ -2401,6 +2401,9 @@
       <c r="N20" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q20" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y20">
         <v>7019000</v>
       </c>
@@ -2454,9 +2457,6 @@
       </c>
       <c r="DO20" s="1">
         <v>46726</v>
-      </c>
-      <c r="DP20" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ20" t="str">
         <v>R-003</v>
@@ -2493,6 +2493,9 @@
       <c r="N21" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q21" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y21">
         <v>7020000</v>
       </c>
@@ -2546,9 +2549,6 @@
       </c>
       <c r="DO21" s="1">
         <v>46392</v>
-      </c>
-      <c r="DP21" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ21" t="str">
         <v>R-004</v>
@@ -2585,6 +2585,9 @@
       <c r="N22" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q22" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y22">
         <v>7021000</v>
       </c>
@@ -2638,9 +2641,6 @@
       </c>
       <c r="DO22" s="1">
         <v>46423</v>
-      </c>
-      <c r="DP22" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ22" t="str">
         <v>R-005</v>
@@ -2677,6 +2677,9 @@
       <c r="N23" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q23" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y23">
         <v>7022000</v>
       </c>
@@ -2715,9 +2718,6 @@
       </c>
       <c r="DO23" s="1">
         <v>46451</v>
-      </c>
-      <c r="DP23" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ23" t="str">
         <v>R-004</v>
@@ -2754,6 +2754,9 @@
       <c r="N24" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q24" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y24">
         <v>7023000</v>
       </c>
@@ -2792,9 +2795,6 @@
       </c>
       <c r="DO24" s="1">
         <v>46482</v>
-      </c>
-      <c r="DP24" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ24" t="str">
         <v>R-004</v>
@@ -2831,6 +2831,9 @@
       <c r="N25" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q25" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y25">
         <v>7024000</v>
       </c>
@@ -2884,9 +2887,6 @@
       </c>
       <c r="DO25" s="1">
         <v>46512</v>
-      </c>
-      <c r="DP25" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ25" t="str">
         <v>R-004</v>
@@ -2923,6 +2923,9 @@
       <c r="N26" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q26" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y26">
         <v>7025000</v>
       </c>
@@ -2976,9 +2979,6 @@
       </c>
       <c r="DO26" s="1">
         <v>46543</v>
-      </c>
-      <c r="DP26" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ26" t="str">
         <v>R-001</v>
@@ -3015,6 +3015,9 @@
       <c r="N27" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q27" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y27">
         <v>7026000</v>
       </c>
@@ -3068,9 +3071,6 @@
       </c>
       <c r="DO27" s="1">
         <v>46573</v>
-      </c>
-      <c r="DP27" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ27" t="str">
         <v>R-001</v>
@@ -3107,6 +3107,9 @@
       <c r="N28" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q28" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y28">
         <v>7027000</v>
       </c>
@@ -3160,9 +3163,6 @@
       </c>
       <c r="DO28" s="1">
         <v>46604</v>
-      </c>
-      <c r="DP28" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ28" t="str">
         <v>R-003</v>
@@ -3199,6 +3199,9 @@
       <c r="N29" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q29" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y29">
         <v>7028000</v>
       </c>
@@ -3252,9 +3255,6 @@
       </c>
       <c r="DO29" s="1">
         <v>46635</v>
-      </c>
-      <c r="DP29" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ29" t="str">
         <v>R-001</v>
@@ -3291,6 +3291,9 @@
       <c r="N30" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q30" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y30">
         <v>7029000</v>
       </c>
@@ -3344,9 +3347,6 @@
       </c>
       <c r="DO30" s="1">
         <v>46665</v>
-      </c>
-      <c r="DP30" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ30" t="str">
         <v>R-001</v>
@@ -3383,6 +3383,9 @@
       <c r="N31" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q31" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y31">
         <v>7030000</v>
       </c>
@@ -3436,9 +3439,6 @@
       </c>
       <c r="DO31" s="1">
         <v>46696</v>
-      </c>
-      <c r="DP31" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ31" t="str">
         <v>R-001</v>
@@ -3475,6 +3475,9 @@
       <c r="N32" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q32" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y32">
         <v>7031000</v>
       </c>
@@ -3528,9 +3531,6 @@
       </c>
       <c r="DO32" s="1">
         <v>46726</v>
-      </c>
-      <c r="DP32" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ32" t="str">
         <v>R-003</v>
@@ -3567,6 +3567,9 @@
       <c r="N33" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q33" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y33">
         <v>7032000</v>
       </c>
@@ -3620,9 +3623,6 @@
       </c>
       <c r="DO33" s="1">
         <v>46392</v>
-      </c>
-      <c r="DP33" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ33" t="str">
         <v>R-002</v>
@@ -3659,6 +3659,9 @@
       <c r="N34" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q34" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y34">
         <v>7033000</v>
       </c>
@@ -3706,9 +3709,6 @@
       </c>
       <c r="DO34" s="1">
         <v>46423</v>
-      </c>
-      <c r="DP34" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ34" t="str">
         <v>R-005</v>
@@ -3745,6 +3745,9 @@
       <c r="N35" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q35" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y35">
         <v>7034000</v>
       </c>
@@ -3792,9 +3795,6 @@
       </c>
       <c r="DO35" s="1">
         <v>46451</v>
-      </c>
-      <c r="DP35" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ35" t="str">
         <v>R-002</v>
@@ -3831,6 +3831,9 @@
       <c r="N36" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q36" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y36">
         <v>7035000</v>
       </c>
@@ -3884,9 +3887,6 @@
       </c>
       <c r="DO36" s="1">
         <v>46482</v>
-      </c>
-      <c r="DP36" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ36" t="str">
         <v>R-004</v>
@@ -3923,6 +3923,9 @@
       <c r="N37" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q37" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y37">
         <v>7036000</v>
       </c>
@@ -3970,9 +3973,6 @@
       </c>
       <c r="DO37" s="1">
         <v>46512</v>
-      </c>
-      <c r="DP37" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ37" t="str">
         <v>R-001</v>
@@ -4009,6 +4009,9 @@
       <c r="N38" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q38" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y38">
         <v>7037000</v>
       </c>
@@ -4056,9 +4059,6 @@
       </c>
       <c r="DO38" s="1">
         <v>46543</v>
-      </c>
-      <c r="DP38" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ38" t="str">
         <v>R-005</v>
@@ -4095,6 +4095,9 @@
       <c r="N39" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q39" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y39">
         <v>7038000</v>
       </c>
@@ -4148,9 +4151,6 @@
       </c>
       <c r="DO39" s="1">
         <v>46573</v>
-      </c>
-      <c r="DP39" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ39" t="str">
         <v>R-004</v>
@@ -4187,6 +4187,9 @@
       <c r="N40" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q40" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y40">
         <v>7039000</v>
       </c>
@@ -4240,9 +4243,6 @@
       </c>
       <c r="DO40" s="1">
         <v>46604</v>
-      </c>
-      <c r="DP40" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ40" t="str">
         <v>R-004</v>
@@ -4279,6 +4279,9 @@
       <c r="N41" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q41" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y41">
         <v>7040000</v>
       </c>
@@ -4332,9 +4335,6 @@
       </c>
       <c r="DO41" s="1">
         <v>46635</v>
-      </c>
-      <c r="DP41" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ41" t="str">
         <v>R-005</v>
@@ -4371,6 +4371,9 @@
       <c r="N42" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q42" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y42">
         <v>7041000</v>
       </c>
@@ -4424,9 +4427,6 @@
       </c>
       <c r="DO42" s="1">
         <v>46665</v>
-      </c>
-      <c r="DP42" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ42" t="str">
         <v>R-005</v>
@@ -4463,6 +4463,9 @@
       <c r="N43" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q43" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y43">
         <v>7042000</v>
       </c>
@@ -4510,9 +4513,6 @@
       </c>
       <c r="DO43" s="1">
         <v>46696</v>
-      </c>
-      <c r="DP43" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ43" t="str">
         <v>R-004</v>
@@ -4549,6 +4549,9 @@
       <c r="N44" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q44" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y44">
         <v>7043000</v>
       </c>
@@ -4596,9 +4599,6 @@
       </c>
       <c r="DO44" s="1">
         <v>46726</v>
-      </c>
-      <c r="DP44" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ44" t="str">
         <v>R-005</v>
@@ -4635,6 +4635,9 @@
       <c r="N45" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q45" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y45">
         <v>7044000</v>
       </c>
@@ -4688,9 +4691,6 @@
       </c>
       <c r="DO45" s="1">
         <v>46392</v>
-      </c>
-      <c r="DP45" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ45" t="str">
         <v>R-004</v>
@@ -4727,6 +4727,9 @@
       <c r="N46" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q46" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y46">
         <v>7045000</v>
       </c>
@@ -4780,9 +4783,6 @@
       </c>
       <c r="DO46" s="1">
         <v>46423</v>
-      </c>
-      <c r="DP46" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ46" t="str">
         <v>R-005</v>
@@ -4819,6 +4819,9 @@
       <c r="N47" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q47" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y47">
         <v>7046000</v>
       </c>
@@ -4872,9 +4875,6 @@
       </c>
       <c r="DO47" s="1">
         <v>46451</v>
-      </c>
-      <c r="DP47" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ47" t="str">
         <v>R-005</v>
@@ -4911,6 +4911,9 @@
       <c r="N48" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q48" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y48">
         <v>7047000</v>
       </c>
@@ -4964,9 +4967,6 @@
       </c>
       <c r="DO48" s="1">
         <v>46482</v>
-      </c>
-      <c r="DP48" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ48" t="str">
         <v>R-004</v>
@@ -5003,6 +5003,9 @@
       <c r="N49" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q49" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y49">
         <v>7048000</v>
       </c>
@@ -5056,9 +5059,6 @@
       </c>
       <c r="DO49" s="1">
         <v>46512</v>
-      </c>
-      <c r="DP49" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ49" t="str">
         <v>R-005</v>
@@ -5095,6 +5095,9 @@
       <c r="N50" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q50" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y50">
         <v>7049000</v>
       </c>
@@ -5142,9 +5145,6 @@
       </c>
       <c r="DO50" s="1">
         <v>46543</v>
-      </c>
-      <c r="DP50" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ50" t="str">
         <v>R-005</v>
@@ -5181,6 +5181,9 @@
       <c r="N51" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q51" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y51">
         <v>7050000</v>
       </c>
@@ -5228,9 +5231,6 @@
       </c>
       <c r="DO51" s="1">
         <v>46573</v>
-      </c>
-      <c r="DP51" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ51" t="str">
         <v>R-005</v>
@@ -5267,6 +5267,9 @@
       <c r="N52" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q52" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y52">
         <v>7051000</v>
       </c>
@@ -5320,9 +5323,6 @@
       </c>
       <c r="DO52" s="1">
         <v>46604</v>
-      </c>
-      <c r="DP52" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ52" t="str">
         <v>R-005</v>
@@ -5359,6 +5359,9 @@
       <c r="N53" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q53" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y53">
         <v>7052000</v>
       </c>
@@ -5412,9 +5415,6 @@
       </c>
       <c r="DO53" s="1">
         <v>46635</v>
-      </c>
-      <c r="DP53" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ53" t="str">
         <v>R-004</v>
@@ -5451,6 +5451,9 @@
       <c r="N54" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q54" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y54">
         <v>7053000</v>
       </c>
@@ -5504,9 +5507,6 @@
       </c>
       <c r="DO54" s="1">
         <v>46665</v>
-      </c>
-      <c r="DP54" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ54" t="str">
         <v>R-004</v>
@@ -5543,6 +5543,9 @@
       <c r="N55" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q55" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y55">
         <v>7054000</v>
       </c>
@@ -5596,9 +5599,6 @@
       </c>
       <c r="DO55" s="1">
         <v>46696</v>
-      </c>
-      <c r="DP55" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ55" t="str">
         <v>R-004</v>
@@ -5635,6 +5635,9 @@
       <c r="N56" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q56" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y56">
         <v>7055000</v>
       </c>
@@ -5688,9 +5691,6 @@
       </c>
       <c r="DO56" s="1">
         <v>46726</v>
-      </c>
-      <c r="DP56" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ56" t="str">
         <v>R-001</v>
@@ -5727,6 +5727,9 @@
       <c r="N57" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q57" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y57">
         <v>7056000</v>
       </c>
@@ -5780,9 +5783,6 @@
       </c>
       <c r="DO57" s="1">
         <v>46392</v>
-      </c>
-      <c r="DP57" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ57" t="str">
         <v>R-001</v>
@@ -5819,6 +5819,9 @@
       <c r="N58" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q58" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y58">
         <v>7057000</v>
       </c>
@@ -5872,9 +5875,6 @@
       </c>
       <c r="DO58" s="1">
         <v>46423</v>
-      </c>
-      <c r="DP58" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ58" t="str">
         <v>R-002</v>
@@ -5911,6 +5911,9 @@
       <c r="N59" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q59" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y59">
         <v>7058000</v>
       </c>
@@ -5964,9 +5967,6 @@
       </c>
       <c r="DO59" s="1">
         <v>46451</v>
-      </c>
-      <c r="DP59" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ59" t="str">
         <v>R-001</v>
@@ -6003,6 +6003,9 @@
       <c r="N60" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q60" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y60">
         <v>7059000</v>
       </c>
@@ -6056,9 +6059,6 @@
       </c>
       <c r="DO60" s="1">
         <v>46482</v>
-      </c>
-      <c r="DP60" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ60" t="str">
         <v>R-004</v>
@@ -6095,6 +6095,9 @@
       <c r="N61" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q61" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y61">
         <v>7060000</v>
       </c>
@@ -6148,9 +6151,6 @@
       </c>
       <c r="DO61" s="1">
         <v>46512</v>
-      </c>
-      <c r="DP61" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ61" t="str">
         <v>R-005</v>
@@ -6187,6 +6187,9 @@
       <c r="N62" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q62" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y62">
         <v>7061000</v>
       </c>
@@ -6240,9 +6243,6 @@
       </c>
       <c r="DO62" s="1">
         <v>46543</v>
-      </c>
-      <c r="DP62" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ62" t="str">
         <v>R-004</v>
@@ -6279,6 +6279,9 @@
       <c r="N63" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q63" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y63">
         <v>7062000</v>
       </c>
@@ -6332,9 +6335,6 @@
       </c>
       <c r="DO63" s="1">
         <v>46573</v>
-      </c>
-      <c r="DP63" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ63" t="str">
         <v>R-004</v>
@@ -6371,6 +6371,9 @@
       <c r="N64" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q64" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y64">
         <v>7063000</v>
       </c>
@@ -6424,9 +6427,6 @@
       </c>
       <c r="DO64" s="1">
         <v>46604</v>
-      </c>
-      <c r="DP64" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ64" t="str">
         <v>R-002</v>
@@ -6463,6 +6463,9 @@
       <c r="N65" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q65" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y65">
         <v>7064000</v>
       </c>
@@ -6516,9 +6519,6 @@
       </c>
       <c r="DO65" s="1">
         <v>46635</v>
-      </c>
-      <c r="DP65" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ65" t="str">
         <v>R-003</v>
@@ -6555,6 +6555,9 @@
       <c r="N66" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q66" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y66">
         <v>7065000</v>
       </c>
@@ -6608,9 +6611,6 @@
       </c>
       <c r="DO66" s="1">
         <v>46665</v>
-      </c>
-      <c r="DP66" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ66" t="str">
         <v>R-003</v>
@@ -6647,6 +6647,9 @@
       <c r="N67" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q67" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y67">
         <v>7066000</v>
       </c>
@@ -6700,9 +6703,6 @@
       </c>
       <c r="DO67" s="1">
         <v>46696</v>
-      </c>
-      <c r="DP67" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ67" t="str">
         <v>R-004</v>
@@ -6739,6 +6739,9 @@
       <c r="N68" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q68" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y68">
         <v>7067000</v>
       </c>
@@ -6792,9 +6795,6 @@
       </c>
       <c r="DO68" s="1">
         <v>46726</v>
-      </c>
-      <c r="DP68" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ68" t="str">
         <v>R-001</v>
@@ -6831,6 +6831,9 @@
       <c r="N69" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q69" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y69">
         <v>7068000</v>
       </c>
@@ -6884,9 +6887,6 @@
       </c>
       <c r="DO69" s="1">
         <v>46392</v>
-      </c>
-      <c r="DP69" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ69" t="str">
         <v>R-001</v>
@@ -6923,6 +6923,9 @@
       <c r="N70" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q70" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y70">
         <v>7069000</v>
       </c>
@@ -6976,9 +6979,6 @@
       </c>
       <c r="DO70" s="1">
         <v>46423</v>
-      </c>
-      <c r="DP70" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ70" t="str">
         <v>R-005</v>
@@ -7015,6 +7015,9 @@
       <c r="N71" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q71" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y71">
         <v>7070000</v>
       </c>
@@ -7068,9 +7071,6 @@
       </c>
       <c r="DO71" s="1">
         <v>46451</v>
-      </c>
-      <c r="DP71" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ71" t="str">
         <v>R-004</v>
@@ -7107,6 +7107,9 @@
       <c r="N72" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q72" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y72">
         <v>7071000</v>
       </c>
@@ -7154,9 +7157,6 @@
       </c>
       <c r="DO72" s="1">
         <v>46482</v>
-      </c>
-      <c r="DP72" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ72" t="str">
         <v>R-004</v>
@@ -7193,6 +7193,9 @@
       <c r="N73" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q73" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y73">
         <v>7072000</v>
       </c>
@@ -7246,9 +7249,6 @@
       </c>
       <c r="DO73" s="1">
         <v>46512</v>
-      </c>
-      <c r="DP73" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ73" t="str">
         <v>R-002</v>
@@ -7285,6 +7285,9 @@
       <c r="N74" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q74" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y74">
         <v>7073000</v>
       </c>
@@ -7338,9 +7341,6 @@
       </c>
       <c r="DO74" s="1">
         <v>46543</v>
-      </c>
-      <c r="DP74" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ74" t="str">
         <v>R-001</v>
@@ -7377,6 +7377,9 @@
       <c r="N75" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q75" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y75">
         <v>7074000</v>
       </c>
@@ -7430,9 +7433,6 @@
       </c>
       <c r="DO75" s="1">
         <v>46573</v>
-      </c>
-      <c r="DP75" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ75" t="str">
         <v>R-003</v>
@@ -7469,6 +7469,9 @@
       <c r="N76" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q76" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y76">
         <v>7075000</v>
       </c>
@@ -7516,9 +7519,6 @@
       </c>
       <c r="DO76" s="1">
         <v>46604</v>
-      </c>
-      <c r="DP76" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ76" t="str">
         <v>R-005</v>
@@ -7555,6 +7555,9 @@
       <c r="N77" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q77" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y77">
         <v>7076000</v>
       </c>
@@ -7608,9 +7611,6 @@
       </c>
       <c r="DO77" s="1">
         <v>46635</v>
-      </c>
-      <c r="DP77" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ77" t="str">
         <v>R-002</v>
@@ -7647,6 +7647,9 @@
       <c r="N78" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q78" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y78">
         <v>7077000</v>
       </c>
@@ -7694,9 +7697,6 @@
       </c>
       <c r="DO78" s="1">
         <v>46665</v>
-      </c>
-      <c r="DP78" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ78" t="str">
         <v>R-005</v>
@@ -7733,6 +7733,9 @@
       <c r="N79" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q79" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y79">
         <v>7078000</v>
       </c>
@@ -7786,9 +7789,6 @@
       </c>
       <c r="DO79" s="1">
         <v>46696</v>
-      </c>
-      <c r="DP79" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ79" t="str">
         <v>R-005</v>
@@ -7825,6 +7825,9 @@
       <c r="N80" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q80" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y80">
         <v>7079000</v>
       </c>
@@ -7878,9 +7881,6 @@
       </c>
       <c r="DO80" s="1">
         <v>46726</v>
-      </c>
-      <c r="DP80" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ80" t="str">
         <v>R-005</v>
@@ -7917,6 +7917,9 @@
       <c r="N81" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q81" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y81">
         <v>7080000</v>
       </c>
@@ -7970,9 +7973,6 @@
       </c>
       <c r="DO81" s="1">
         <v>46392</v>
-      </c>
-      <c r="DP81" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ81" t="str">
         <v>R-002</v>
@@ -8009,6 +8009,9 @@
       <c r="N82" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q82" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y82">
         <v>7081000</v>
       </c>
@@ -8062,9 +8065,6 @@
       </c>
       <c r="DO82" s="1">
         <v>46423</v>
-      </c>
-      <c r="DP82" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ82" t="str">
         <v>R-001</v>
@@ -8101,6 +8101,9 @@
       <c r="N83" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q83" t="str">
+        <v>Improvement.On Platform</v>
+      </c>
       <c r="Y83">
         <v>7082000</v>
       </c>
@@ -8148,9 +8151,6 @@
       </c>
       <c r="DO83" s="1">
         <v>46451</v>
-      </c>
-      <c r="DP83" t="str">
-        <v>Improvement.On Platform</v>
       </c>
       <c r="DQ83" t="str">
         <v>R-003</v>
@@ -8187,6 +8187,9 @@
       <c r="N84" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q84" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y84">
         <v>7083000</v>
       </c>
@@ -8240,9 +8243,6 @@
       </c>
       <c r="DO84" s="1">
         <v>46482</v>
-      </c>
-      <c r="DP84" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ84" t="str">
         <v>R-003</v>
@@ -8279,6 +8279,9 @@
       <c r="N85" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q85" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y85">
         <v>7084000</v>
       </c>
@@ -8332,9 +8335,6 @@
       </c>
       <c r="DO85" s="1">
         <v>46512</v>
-      </c>
-      <c r="DP85" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ85" t="str">
         <v>R-001</v>
@@ -8371,6 +8371,9 @@
       <c r="N86" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q86" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y86">
         <v>7085000</v>
       </c>
@@ -8424,9 +8427,6 @@
       </c>
       <c r="DO86" s="1">
         <v>46543</v>
-      </c>
-      <c r="DP86" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ86" t="str">
         <v>R-004</v>
@@ -8463,6 +8463,9 @@
       <c r="N87" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q87" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y87">
         <v>7086000</v>
       </c>
@@ -8516,9 +8519,6 @@
       </c>
       <c r="DO87" s="1">
         <v>46573</v>
-      </c>
-      <c r="DP87" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ87" t="str">
         <v>R-003</v>
@@ -8555,6 +8555,9 @@
       <c r="N88" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q88" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y88">
         <v>7087000</v>
       </c>
@@ -8608,9 +8611,6 @@
       </c>
       <c r="DO88" s="1">
         <v>46604</v>
-      </c>
-      <c r="DP88" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ88" t="str">
         <v>R-004</v>
@@ -8647,6 +8647,9 @@
       <c r="N89" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q89" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y89">
         <v>7088000</v>
       </c>
@@ -8700,9 +8703,6 @@
       </c>
       <c r="DO89" s="1">
         <v>46635</v>
-      </c>
-      <c r="DP89" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ89" t="str">
         <v>R-005</v>
@@ -8739,6 +8739,9 @@
       <c r="N90" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q90" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y90">
         <v>7089000</v>
       </c>
@@ -8792,9 +8795,6 @@
       </c>
       <c r="DO90" s="1">
         <v>46665</v>
-      </c>
-      <c r="DP90" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ90" t="str">
         <v>R-002</v>
@@ -8831,6 +8831,9 @@
       <c r="N91" t="str">
         <v>Alpha</v>
       </c>
+      <c r="Q91" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y91">
         <v>7090000</v>
       </c>
@@ -8884,9 +8887,6 @@
       </c>
       <c r="DO91" s="1">
         <v>46696</v>
-      </c>
-      <c r="DP91" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ91" t="str">
         <v>R-005</v>
@@ -8923,6 +8923,9 @@
       <c r="N92" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q92" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y92">
         <v>7091000</v>
       </c>
@@ -8976,9 +8979,6 @@
       </c>
       <c r="DO92" s="1">
         <v>46726</v>
-      </c>
-      <c r="DP92" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ92" t="str">
         <v>R-005</v>
@@ -9015,6 +9015,9 @@
       <c r="N93" t="str">
         <v>Gamma</v>
       </c>
+      <c r="Q93" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y93">
         <v>7092000</v>
       </c>
@@ -9068,9 +9071,6 @@
       </c>
       <c r="DO93" s="1">
         <v>46392</v>
-      </c>
-      <c r="DP93" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ93" t="str">
         <v>R-002</v>
@@ -9107,6 +9107,9 @@
       <c r="N94" t="str">
         <v>Beta</v>
       </c>
+      <c r="Q94" t="str">
+        <v>Compliance.On Platform</v>
+      </c>
       <c r="Y94">
         <v>7093000</v>
       </c>
@@ -9160,9 +9163,6 @@
       </c>
       <c r="DO94" s="1">
         <v>46423</v>
-      </c>
-      <c r="DP94" t="str">
-        <v>Compliance.On Platform</v>
       </c>
       <c r="DQ94" t="str">
         <v>R-003</v>
@@ -9199,6 +9199,9 @@
       <c r="N95" t="str">
         <v>Delta</v>
       </c>
+      <c r="Q95" t="str">
+        <v>Product Expansion/Refresh.On Platform</v>
+      </c>
       <c r="Y95">
         <v>7094000</v>
       </c>
@@ -9252,9 +9255,6 @@
       </c>
       <c r="DO95" s="1">
         <v>46451</v>
-      </c>
-      <c r="DP95" t="str">
-        <v>Product Expansion/Refresh.On Platform</v>
       </c>
       <c r="DQ95" t="str">
         <v>R-005</v>
